--- a/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Class_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Bacteria/Sample_name/Bacteria_Summary_Class_by_Sample_name.xlsx
@@ -829,10 +829,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>19.111645461561</v>
+        <v>19.1100993570936</v>
       </c>
       <c r="D2" t="n">
-        <v>0.622604635229222</v>
+        <v>0.625537254589811</v>
       </c>
     </row>
     <row r="3">
@@ -843,10 +843,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>12.3175707712071</v>
+        <v>12.3142029661218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.465890434335378</v>
+        <v>0.4656264873564</v>
       </c>
     </row>
     <row r="4">
@@ -857,10 +857,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>10.833248956956</v>
+        <v>10.8369586056025</v>
       </c>
       <c r="D4" t="n">
-        <v>0.218799265895467</v>
+        <v>0.218890566464749</v>
       </c>
     </row>
     <row r="5">
@@ -871,10 +871,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.0871993316727</v>
+        <v>8.0878346289725</v>
       </c>
       <c r="D5" t="n">
-        <v>0.155470047538379</v>
+        <v>0.155472682351987</v>
       </c>
     </row>
     <row r="6">
@@ -885,10 +885,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>8.028736127089</v>
+        <v>8.02835388683251</v>
       </c>
       <c r="D6" t="n">
-        <v>0.22815794261945</v>
+        <v>0.228047101254038</v>
       </c>
     </row>
     <row r="7">
@@ -899,10 +899,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.97917800897689</v>
+        <v>4.97978907021735</v>
       </c>
       <c r="D7" t="n">
-        <v>0.119515595406653</v>
+        <v>0.119487717840719</v>
       </c>
     </row>
     <row r="8">
@@ -913,10 +913,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.9152610825326</v>
+        <v>4.92120017515589</v>
       </c>
       <c r="D8" t="n">
-        <v>0.734079069717766</v>
+        <v>0.735248137290882</v>
       </c>
     </row>
     <row r="9">
@@ -927,10 +927,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.75776899905221</v>
+        <v>3.74539333974415</v>
       </c>
       <c r="D9" t="n">
-        <v>0.91458931157173</v>
+        <v>0.99792186077195</v>
       </c>
     </row>
     <row r="10">
@@ -941,10 +941,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.21746502149542</v>
+        <v>2.218745733239</v>
       </c>
       <c r="D10" t="n">
-        <v>0.250100382956219</v>
+        <v>0.250249846884511</v>
       </c>
     </row>
     <row r="11">
@@ -955,10 +955,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.15894967249864</v>
+        <v>2.15910343882614</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0891871554359283</v>
+        <v>0.0891807023663215</v>
       </c>
     </row>
     <row r="12">
@@ -969,10 +969,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.89041475746432</v>
+        <v>1.89088521201451</v>
       </c>
       <c r="D12" t="n">
-        <v>0.285295396610977</v>
+        <v>0.285391683730003</v>
       </c>
     </row>
     <row r="13">
@@ -983,10 +983,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.50564927210976</v>
+        <v>1.5054470119865</v>
       </c>
       <c r="D13" t="n">
-        <v>0.256379238498371</v>
+        <v>0.25636445455321</v>
       </c>
     </row>
     <row r="14">
@@ -997,10 +997,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4103647589089</v>
+        <v>1.41128133343075</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0491918772283142</v>
+        <v>0.0492482126452453</v>
       </c>
     </row>
     <row r="15">
@@ -1011,10 +1011,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.23528941487672</v>
+        <v>1.23454600774369</v>
       </c>
       <c r="D15" t="n">
-        <v>0.181433498640131</v>
+        <v>0.181319744290491</v>
       </c>
     </row>
     <row r="16">
@@ -1025,10 +1025,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.22598699751949</v>
+        <v>1.22696488686705</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0706217134763366</v>
+        <v>0.0707036435439333</v>
       </c>
     </row>
     <row r="17">
@@ -1039,10 +1039,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.13436578369424</v>
+        <v>1.13445349236647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.156984287098916</v>
+        <v>0.157018752733904</v>
       </c>
     </row>
     <row r="18">
@@ -1053,10 +1053,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.11595841296818</v>
+        <v>1.11619982446404</v>
       </c>
       <c r="D18" t="n">
-        <v>0.134571441637726</v>
+        <v>0.134596346289172</v>
       </c>
     </row>
     <row r="19">
@@ -1067,10 +1067,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.07809169025661</v>
+        <v>1.07756858112191</v>
       </c>
       <c r="D19" t="n">
-        <v>0.42393483508724</v>
+        <v>0.423728975821153</v>
       </c>
     </row>
     <row r="20">
@@ -1081,10 +1081,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.835334189022212</v>
+        <v>0.836043950484312</v>
       </c>
       <c r="D20" t="n">
-        <v>0.131596510084183</v>
+        <v>0.131785520769416</v>
       </c>
     </row>
     <row r="21">
@@ -1095,10 +1095,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.778065029755571</v>
+        <v>0.778425771423493</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0293551033869069</v>
+        <v>0.0293645450508629</v>
       </c>
     </row>
     <row r="22">
@@ -1109,10 +1109,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.756458102539692</v>
+        <v>0.756518834467398</v>
       </c>
       <c r="D22" t="n">
-        <v>0.106151263535116</v>
+        <v>0.106162700491151</v>
       </c>
     </row>
     <row r="23">
@@ -1123,10 +1123,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.749659009917814</v>
+        <v>0.749516216573399</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0571783094222008</v>
+        <v>0.0571555031807758</v>
       </c>
     </row>
     <row r="24">
@@ -1137,10 +1137,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.714826822625599</v>
+        <v>0.714978920984788</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0135842222527626</v>
+        <v>0.0135942961273402</v>
       </c>
     </row>
     <row r="25">
@@ -1151,10 +1151,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.636716793139607</v>
+        <v>0.636804673660586</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0864263942846487</v>
+        <v>0.0864007782948526</v>
       </c>
     </row>
     <row r="26">
@@ -1165,10 +1165,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.513152663995786</v>
+        <v>0.51326290197232</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0356041790420883</v>
+        <v>0.0356002623511337</v>
       </c>
     </row>
     <row r="27">
@@ -1179,10 +1179,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.510338886355404</v>
+        <v>0.510440112571331</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0269307942548132</v>
+        <v>0.0269465932822435</v>
       </c>
     </row>
     <row r="28">
@@ -1193,10 +1193,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.466972583887116</v>
+        <v>0.466936665839005</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0355597834704603</v>
+        <v>0.0355502792107136</v>
       </c>
     </row>
     <row r="29">
@@ -1207,10 +1207,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4088185973569</v>
+        <v>0.408909389303892</v>
       </c>
       <c r="D29" t="n">
-        <v>0.288546878914999</v>
+        <v>0.288611410677035</v>
       </c>
     </row>
     <row r="30">
@@ -1221,10 +1221,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.383103375171294</v>
+        <v>0.38291142151032</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0517998879540366</v>
+        <v>0.0517687276511165</v>
       </c>
     </row>
     <row r="31">
@@ -1235,10 +1235,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.339318121250625</v>
+        <v>0.339147527832547</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0244474757887373</v>
+        <v>0.0244331327467964</v>
       </c>
     </row>
     <row r="32">
@@ -1249,10 +1249,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.278657722856185</v>
+        <v>0.278767590229374</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0792187171209087</v>
+        <v>0.0792396794698137</v>
       </c>
     </row>
     <row r="33">
@@ -1263,10 +1263,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.271640061510356</v>
+        <v>0.271861567131855</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0725397552414903</v>
+        <v>0.0725781789921531</v>
       </c>
     </row>
     <row r="34">
@@ -1277,10 +1277,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.253648106070882</v>
+        <v>0.253722949129293</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0450750799753571</v>
+        <v>0.0450911301614012</v>
       </c>
     </row>
     <row r="35">
@@ -1291,10 +1291,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.249904372955817</v>
+        <v>0.249893879789821</v>
       </c>
       <c r="D35" t="n">
-        <v>0.03067969055944</v>
+        <v>0.0306659537196522</v>
       </c>
     </row>
     <row r="36">
@@ -1305,10 +1305,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.24651846614152</v>
+        <v>0.246721509220616</v>
       </c>
       <c r="D36" t="n">
-        <v>0.016108691495076</v>
+        <v>0.0161258643029431</v>
       </c>
     </row>
     <row r="37">
@@ -1319,10 +1319,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.230226564505593</v>
+        <v>0.230507494857573</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0779945104442297</v>
+        <v>0.0780930687904856</v>
       </c>
     </row>
     <row r="38">
@@ -1333,10 +1333,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.224707900679495</v>
+        <v>0.224925583357573</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0481322120250368</v>
+        <v>0.048230329885155</v>
       </c>
     </row>
     <row r="39">
@@ -1347,10 +1347,10 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.201662483669726</v>
+        <v>0.201956720680122</v>
       </c>
       <c r="D39" t="n">
-        <v>0.113021158477521</v>
+        <v>0.113189572684481</v>
       </c>
     </row>
     <row r="40">
@@ -1361,10 +1361,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.196306315081387</v>
+        <v>0.196210227802146</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0502835718087378</v>
+        <v>0.0502543582644417</v>
       </c>
     </row>
     <row r="41">
@@ -1375,10 +1375,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.181341093044664</v>
+        <v>0.181297270181016</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0366730244195918</v>
+        <v>0.0366559937521825</v>
       </c>
     </row>
     <row r="42">
@@ -1389,10 +1389,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.172420469334147</v>
+        <v>0.172564304036702</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0178550803077801</v>
+        <v>0.0178692640557115</v>
       </c>
     </row>
     <row r="43">
@@ -1403,10 +1403,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.17151734381582</v>
+        <v>0.171684741662243</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0191479318986101</v>
+        <v>0.0191784685597733</v>
       </c>
     </row>
     <row r="44">
@@ -1417,10 +1417,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.167944749899349</v>
+        <v>0.167920181042837</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0203377159953992</v>
+        <v>0.020325198869402</v>
       </c>
     </row>
     <row r="45">
@@ -1431,10 +1431,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.16769110016552</v>
+        <v>0.167749934116403</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0134170834047453</v>
+        <v>0.0134259753477926</v>
       </c>
     </row>
     <row r="46">
@@ -1445,10 +1445,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.164689681219497</v>
+        <v>0.16464510137238</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0314254701685319</v>
+        <v>0.031409205840761</v>
       </c>
     </row>
     <row r="47">
@@ -1459,7 +1459,7 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.155636591615676</v>
+        <v>0.155646191017779</v>
       </c>
       <c r="D47"/>
     </row>
@@ -1471,10 +1471,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.137844176960394</v>
+        <v>0.137924131063222</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0128841280713531</v>
+        <v>0.0128931343736333</v>
       </c>
     </row>
     <row r="49">
@@ -1485,10 +1485,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.136854555704109</v>
+        <v>0.136954032102515</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0099182769151916</v>
+        <v>0.00992803048451358</v>
       </c>
     </row>
     <row r="50">
@@ -1499,10 +1499,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.110906171094441</v>
+        <v>0.110935645896679</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0191480991970206</v>
+        <v>0.0191533162734404</v>
       </c>
     </row>
     <row r="51">
@@ -1513,10 +1513,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.109230533673769</v>
+        <v>0.10920905598049</v>
       </c>
       <c r="D51" t="n">
-        <v>0.055621362907144</v>
+        <v>0.0556131837228267</v>
       </c>
     </row>
     <row r="52">
@@ -1527,10 +1527,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.105939654299032</v>
+        <v>0.106073371239914</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0346530973988826</v>
+        <v>0.0347010905517151</v>
       </c>
     </row>
     <row r="53">
@@ -1541,10 +1541,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.105448800808803</v>
+        <v>0.105455041134451</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0413991437900736</v>
+        <v>0.0414242815338174</v>
       </c>
     </row>
     <row r="54">
@@ -1555,7 +1555,7 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0898734498482633</v>
+        <v>0.0900476662449236</v>
       </c>
       <c r="D54"/>
     </row>
@@ -1567,7 +1567,7 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0824633863583317</v>
+        <v>0.082594889673945</v>
       </c>
       <c r="D55"/>
     </row>
@@ -1579,10 +1579,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0819198271588612</v>
+        <v>0.0819137336845923</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0463842409437896</v>
+        <v>0.0463530331911918</v>
       </c>
     </row>
     <row r="57">
@@ -1593,10 +1593,10 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0795975765640973</v>
+        <v>0.0796511043519289</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00612752082791103</v>
+        <v>0.00613073541590049</v>
       </c>
     </row>
     <row r="58">
@@ -1607,10 +1607,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0779468045632271</v>
+        <v>0.0779402209067128</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0104797531351658</v>
+        <v>0.0104788399728233</v>
       </c>
     </row>
     <row r="59">
@@ -1621,10 +1621,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.074382854607591</v>
+        <v>0.0744314513860011</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00497512625900137</v>
+        <v>0.00497928913366611</v>
       </c>
     </row>
     <row r="60">
@@ -1635,10 +1635,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0715220403491635</v>
+        <v>0.0715238470417609</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00451689341813659</v>
+        <v>0.0045150192905916</v>
       </c>
     </row>
     <row r="61">
@@ -1649,10 +1649,10 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0695745671991399</v>
+        <v>0.0696031139254447</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0095372186779335</v>
+        <v>0.0095375980362307</v>
       </c>
     </row>
     <row r="62">
@@ -1663,10 +1663,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0682203840881914</v>
+        <v>0.0681926728321165</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0142143920882456</v>
+        <v>0.0142057188553385</v>
       </c>
     </row>
     <row r="63">
@@ -1677,10 +1677,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0658554188557988</v>
+        <v>0.0658599253254688</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0193352168764477</v>
+        <v>0.0193275043911341</v>
       </c>
     </row>
     <row r="64">
@@ -1691,10 +1691,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0623446797759473</v>
+        <v>0.0623799883978994</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0107114341897541</v>
+        <v>0.0107249026877623</v>
       </c>
     </row>
     <row r="65">
@@ -1705,10 +1705,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0618597760249946</v>
+        <v>0.0618449586831298</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0145197697950224</v>
+        <v>0.0145115191656285</v>
       </c>
     </row>
     <row r="66">
@@ -1719,10 +1719,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0555839798112815</v>
+        <v>0.0556503826261249</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00561186190411238</v>
+        <v>0.00562248600302131</v>
       </c>
     </row>
     <row r="67">
@@ -1733,10 +1733,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0507339880982861</v>
+        <v>0.0507395300984238</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0176436675496659</v>
+        <v>0.0176397754207485</v>
       </c>
     </row>
     <row r="68">
@@ -1747,10 +1747,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0503580319316139</v>
+        <v>0.0504466044147872</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0154330602509476</v>
+        <v>0.0154650854389714</v>
       </c>
     </row>
     <row r="69">
@@ -1761,10 +1761,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0475084997259635</v>
+        <v>0.0475787150042916</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00765797872765387</v>
+        <v>0.00767280656412586</v>
       </c>
     </row>
     <row r="70">
@@ -1775,10 +1775,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0471690278095655</v>
+        <v>0.04719362599277</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0141529111462473</v>
+        <v>0.0141691878422907</v>
       </c>
     </row>
     <row r="71">
@@ -1789,10 +1789,10 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0465713035308417</v>
+        <v>0.0465814101920786</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00274360388544192</v>
+        <v>0.0027447131064284</v>
       </c>
     </row>
     <row r="72">
@@ -1803,10 +1803,10 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0429041873413532</v>
+        <v>0.0429446890274804</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00545126739233153</v>
+        <v>0.00545621228072605</v>
       </c>
     </row>
     <row r="73">
@@ -1817,10 +1817,10 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0401596736468768</v>
+        <v>0.040181023270795</v>
       </c>
       <c r="D73" t="n">
-        <v>0.000909775279952365</v>
+        <v>0.000910029833040341</v>
       </c>
     </row>
     <row r="74">
@@ -1831,10 +1831,10 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0351925955553089</v>
+        <v>0.03519865020563</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00226274778459942</v>
+        <v>0.00226330298748901</v>
       </c>
     </row>
     <row r="75">
@@ -1845,10 +1845,10 @@
         <v>78</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0344223849672116</v>
+        <v>0.0344735721920936</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0230481661767679</v>
+        <v>0.0230851684943008</v>
       </c>
     </row>
     <row r="76">
@@ -1859,10 +1859,10 @@
         <v>79</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0333910032767665</v>
+        <v>0.0334073832857585</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0159828163430173</v>
+        <v>0.0159679892239189</v>
       </c>
     </row>
     <row r="77">
@@ -1873,10 +1873,10 @@
         <v>80</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0295511762594413</v>
+        <v>0.0295482472732821</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00688078635279297</v>
+        <v>0.00687670322745282</v>
       </c>
     </row>
     <row r="78">
@@ -1887,10 +1887,10 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>0.026677227670915</v>
+        <v>0.0267073954306749</v>
       </c>
       <c r="D78" t="n">
-        <v>0.011737534200288</v>
+        <v>0.0117557821068336</v>
       </c>
     </row>
     <row r="79">
@@ -1901,10 +1901,10 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0259404142042226</v>
+        <v>0.0259715472656145</v>
       </c>
       <c r="D79" t="n">
-        <v>0.000584390141011398</v>
+        <v>0.000559194759903937</v>
       </c>
     </row>
     <row r="80">
@@ -1915,10 +1915,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0257540638797449</v>
+        <v>0.0257635487143075</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00585574320967161</v>
+        <v>0.00585691730027091</v>
       </c>
     </row>
     <row r="81">
@@ -1929,10 +1929,10 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0243285961567221</v>
+        <v>0.0243343159503515</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00553670954351923</v>
+        <v>0.00553543484028905</v>
       </c>
     </row>
     <row r="82">
@@ -1943,10 +1943,10 @@
         <v>85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0234303539149701</v>
+        <v>0.0234492002165133</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00430143010827285</v>
+        <v>0.00430577401358512</v>
       </c>
     </row>
     <row r="83">
@@ -1957,10 +1957,10 @@
         <v>86</v>
       </c>
       <c r="C83" t="n">
-        <v>0.021949542390762</v>
+        <v>0.0219461470389867</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00525866057548123</v>
+        <v>0.00525821332332612</v>
       </c>
     </row>
     <row r="84">
@@ -1971,7 +1971,7 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0207110985476066</v>
+        <v>0.0207233421792403</v>
       </c>
       <c r="D84"/>
     </row>
@@ -1983,10 +1983,10 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0178640921746675</v>
+        <v>0.0178717201851091</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00654839271695026</v>
+        <v>0.00655266277632226</v>
       </c>
     </row>
     <row r="86">
@@ -1997,7 +1997,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0170984842150663</v>
+        <v>0.0171155657968628</v>
       </c>
       <c r="D86"/>
     </row>
@@ -2009,10 +2009,10 @@
         <v>90</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0157348713286623</v>
+        <v>0.0157339012021377</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00281262510809732</v>
+        <v>0.00281091466530258</v>
       </c>
     </row>
     <row r="88">
@@ -2023,10 +2023,10 @@
         <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0156850282298261</v>
+        <v>0.0156957569154902</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00169527959898111</v>
+        <v>0.00169641307580861</v>
       </c>
     </row>
     <row r="89">
@@ -2037,10 +2037,10 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0154673575797283</v>
+        <v>0.0154790637106093</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00913730738070523</v>
+        <v>0.00914187046908357</v>
       </c>
     </row>
     <row r="90">
@@ -2051,7 +2051,7 @@
         <v>93</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0139061684456853</v>
+        <v>0.0139227768153937</v>
       </c>
       <c r="D90"/>
     </row>
@@ -2063,10 +2063,10 @@
         <v>94</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0137969963429416</v>
+        <v>0.0137976298984666</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00169287131451369</v>
+        <v>0.00169218891279535</v>
       </c>
     </row>
     <row r="92">
@@ -2077,7 +2077,7 @@
         <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0137013514776073</v>
+        <v>0.0137009790074467</v>
       </c>
       <c r="D92"/>
     </row>
@@ -2089,7 +2089,7 @@
         <v>96</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0134256428047656</v>
+        <v>0.0134533216169343</v>
       </c>
       <c r="D93"/>
     </row>
@@ -2101,10 +2101,10 @@
         <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0128806242352841</v>
+        <v>0.0128961906537249</v>
       </c>
       <c r="D94" t="n">
-        <v>0.000372288747805415</v>
+        <v>0.00037590358487797</v>
       </c>
     </row>
     <row r="95">
@@ -2115,7 +2115,7 @@
         <v>98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0124492681378108</v>
+        <v>0.0124706574794492</v>
       </c>
       <c r="D95"/>
     </row>
@@ -2127,10 +2127,10 @@
         <v>99</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0111651909170047</v>
+        <v>0.0111704421556242</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00171891274424661</v>
+        <v>0.0017213366312229</v>
       </c>
     </row>
     <row r="97">
@@ -2141,10 +2141,10 @@
         <v>100</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0105877855592029</v>
+        <v>0.0105918830784453</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00228399653386542</v>
+        <v>0.00228542298399814</v>
       </c>
     </row>
     <row r="98">
@@ -2155,10 +2155,10 @@
         <v>101</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00956370071881259</v>
+        <v>0.00956664318571698</v>
       </c>
       <c r="D98" t="n">
-        <v>0.00195416013574069</v>
+        <v>0.00195385854037871</v>
       </c>
     </row>
     <row r="99">
@@ -2169,7 +2169,7 @@
         <v>102</v>
       </c>
       <c r="C99" t="n">
-        <v>0.00939003568750717</v>
+        <v>0.00938624314769026</v>
       </c>
       <c r="D99"/>
     </row>
@@ -2181,10 +2181,10 @@
         <v>103</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00874067216224134</v>
+        <v>0.0087355464931163</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00569121539595544</v>
+        <v>0.00568742084255541</v>
       </c>
     </row>
     <row r="101">
@@ -2195,10 +2195,10 @@
         <v>104</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0081083159105649</v>
+        <v>0.00811615059140891</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00128336424949767</v>
+        <v>0.00128264157689131</v>
       </c>
     </row>
     <row r="102">
@@ -2209,7 +2209,7 @@
         <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00637284431944258</v>
+        <v>0.00637121776090612</v>
       </c>
       <c r="D102"/>
     </row>
@@ -2221,7 +2221,7 @@
         <v>106</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00602152905410947</v>
+        <v>0.00602259019985636</v>
       </c>
       <c r="D103"/>
     </row>
@@ -2233,10 +2233,10 @@
         <v>107</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00602035033217753</v>
+        <v>0.00601922452750512</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00110838153685583</v>
+        <v>0.0011078502016437</v>
       </c>
     </row>
     <row r="105">
@@ -2247,7 +2247,7 @@
         <v>108</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00529599764019417</v>
+        <v>0.00529420260850783</v>
       </c>
       <c r="D105"/>
     </row>
@@ -2259,10 +2259,10 @@
         <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00500530235993212</v>
+        <v>0.0050069424733291</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00300775968935928</v>
+        <v>0.00300925158530516</v>
       </c>
     </row>
     <row r="107">
@@ -2273,7 +2273,7 @@
         <v>110</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00472970594632202</v>
+        <v>0.00473258408216348</v>
       </c>
       <c r="D107"/>
     </row>
@@ -2285,10 +2285,10 @@
         <v>111</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00400002094083704</v>
+        <v>0.00399881141505295</v>
       </c>
       <c r="D108" t="n">
-        <v>0.00110559438793898</v>
+        <v>0.00110581576899999</v>
       </c>
     </row>
     <row r="109">
@@ -2299,10 +2299,10 @@
         <v>112</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00380345502628255</v>
+        <v>0.00380472430946451</v>
       </c>
       <c r="D109" t="n">
-        <v>0.000427683143886077</v>
+        <v>0.000428141058337183</v>
       </c>
     </row>
     <row r="110">
@@ -2313,10 +2313,10 @@
         <v>113</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00308701661012792</v>
+        <v>0.00308508746622922</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00111988265544537</v>
+        <v>0.00111918281638882</v>
       </c>
     </row>
     <row r="111">
@@ -2327,7 +2327,7 @@
         <v>114</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0029804264697113</v>
+        <v>0.00298860485882687</v>
       </c>
       <c r="D111"/>
     </row>
@@ -2339,10 +2339,10 @@
         <v>115</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0029340634070551</v>
+        <v>0.00293352002134484</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000782560473398655</v>
+        <v>0.000782983725386847</v>
       </c>
     </row>
     <row r="113">
@@ -2353,7 +2353,7 @@
         <v>116</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00282253386044751</v>
+        <v>0.00282335034638076</v>
       </c>
       <c r="D113"/>
     </row>
@@ -2365,7 +2365,7 @@
         <v>117</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00234891216227196</v>
+        <v>0.0023486222612377</v>
       </c>
       <c r="D114"/>
     </row>
@@ -2377,10 +2377,10 @@
         <v>118</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00174619234774136</v>
+        <v>0.00174779365200135</v>
       </c>
       <c r="D115" t="n">
-        <v>0.000437459123487345</v>
+        <v>0.000439089657549766</v>
       </c>
     </row>
     <row r="116">
@@ -2391,7 +2391,7 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00173025153685231</v>
+        <v>0.00173079700662756</v>
       </c>
       <c r="D116"/>
     </row>
@@ -2403,7 +2403,7 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00163455054190216</v>
+        <v>0.00164020432583989</v>
       </c>
       <c r="D117"/>
     </row>
@@ -2415,7 +2415,7 @@
         <v>121</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00161265999173761</v>
+        <v>0.00161412036511775</v>
       </c>
       <c r="D118"/>
     </row>
@@ -2427,10 +2427,10 @@
         <v>122</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00158700875731402</v>
+        <v>0.00159011190234553</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0000335774286400194</v>
+        <v>0.0000354206923389287</v>
       </c>
     </row>
     <row r="120">
@@ -2441,10 +2441,10 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00141861990989441</v>
+        <v>0.00142076248853874</v>
       </c>
       <c r="D120" t="n">
-        <v>0.000309658508569068</v>
+        <v>0.00030875102930148</v>
       </c>
     </row>
     <row r="121">
@@ -2455,7 +2455,7 @@
         <v>124</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00140290361746858</v>
+        <v>0.00140258785784202</v>
       </c>
       <c r="D121"/>
     </row>
@@ -2467,7 +2467,7 @@
         <v>125</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00128295462849001</v>
+        <v>0.00128333086752958</v>
       </c>
       <c r="D122"/>
     </row>
@@ -2479,7 +2479,7 @@
         <v>126</v>
       </c>
       <c r="C123" t="n">
-        <v>0.00123771415814994</v>
+        <v>0.00123828695256209</v>
       </c>
       <c r="D123"/>
     </row>
@@ -2491,7 +2491,7 @@
         <v>127</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0011462790140011</v>
+        <v>0.00114589924652043</v>
       </c>
       <c r="D124"/>
     </row>
@@ -2503,7 +2503,7 @@
         <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00110917733795298</v>
+        <v>0.00111123282130261</v>
       </c>
       <c r="D125"/>
     </row>
@@ -2515,10 +2515,10 @@
         <v>129</v>
       </c>
       <c r="C126" t="n">
-        <v>0.000910366238766222</v>
+        <v>0.000912770341657549</v>
       </c>
       <c r="D126" t="n">
-        <v>0.000280883525396474</v>
+        <v>0.000282413582814303</v>
       </c>
     </row>
     <row r="127">
@@ -2529,7 +2529,7 @@
         <v>130</v>
       </c>
       <c r="C127" t="n">
-        <v>0.000865125768426153</v>
+        <v>0.000865370456044187</v>
       </c>
       <c r="D127"/>
     </row>
@@ -2541,7 +2541,7 @@
         <v>131</v>
       </c>
       <c r="C128" t="n">
-        <v>0.000865125768426153</v>
+        <v>0.000865370456044187</v>
       </c>
       <c r="D128"/>
     </row>
@@ -2553,7 +2553,7 @@
         <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>0.000519086686978853</v>
+        <v>0.000519211054718674</v>
       </c>
       <c r="D129"/>
     </row>
@@ -2565,7 +2565,7 @@
         <v>133</v>
       </c>
       <c r="C130" t="n">
-        <v>0.000490348323685906</v>
+        <v>0.000492061297751968</v>
       </c>
       <c r="D130"/>
     </row>
@@ -2577,7 +2577,7 @@
         <v>134</v>
       </c>
       <c r="C131" t="n">
-        <v>0.000326898882457271</v>
+        <v>0.000328040865167978</v>
       </c>
       <c r="D131"/>
     </row>
@@ -2589,7 +2589,7 @@
         <v>135</v>
       </c>
       <c r="C132" t="n">
-        <v>0.000326898882457271</v>
+        <v>0.000328040865167978</v>
       </c>
       <c r="D132"/>
     </row>
@@ -2601,7 +2601,7 @@
         <v>136</v>
       </c>
       <c r="C133" t="n">
-        <v>0.00025656847385168</v>
+        <v>0.000256688611321592</v>
       </c>
       <c r="D133"/>
     </row>
@@ -2638,10 +2638,10 @@
         <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>22.5669687709169</v>
+        <v>23.3274093077896</v>
       </c>
       <c r="D2" t="n">
-        <v>7.22096467611576</v>
+        <v>7.4641192228489</v>
       </c>
     </row>
     <row r="3">
@@ -2652,10 +2652,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>17.2289684631037</v>
+        <v>16.7914816095962</v>
       </c>
       <c r="D3" t="n">
-        <v>1.35640166310062</v>
+        <v>1.31249597273238</v>
       </c>
     </row>
     <row r="4">
@@ -2666,10 +2666,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>15.3572206618281</v>
+        <v>15.7930064167728</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44600602724275</v>
+        <v>1.48639201031792</v>
       </c>
     </row>
     <row r="5">
@@ -2680,10 +2680,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>12.6389195694795</v>
+        <v>12.9681573279387</v>
       </c>
       <c r="D5" t="n">
-        <v>0.397573861014177</v>
+        <v>0.410512041188806</v>
       </c>
     </row>
     <row r="6">
@@ -2694,10 +2694,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>7.3550727669747</v>
+        <v>7.50833741590952</v>
       </c>
       <c r="D6" t="n">
-        <v>0.476065201821035</v>
+        <v>0.48626344077908</v>
       </c>
     </row>
     <row r="7">
@@ -2705,13 +2705,13 @@
         <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>3.68243771737081</v>
+        <v>3.45797997640481</v>
       </c>
       <c r="D7" t="n">
-        <v>0.403658092549487</v>
+        <v>0.475275462469982</v>
       </c>
     </row>
     <row r="8">
@@ -2719,13 +2719,13 @@
         <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>3.39614730115027</v>
+        <v>2.76647323949013</v>
       </c>
       <c r="D8" t="n">
-        <v>0.464943546488048</v>
+        <v>0.137263900503412</v>
       </c>
     </row>
     <row r="9">
@@ -2733,13 +2733,13 @@
         <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72202037458593</v>
+        <v>2.08373589957777</v>
       </c>
       <c r="D9" t="n">
-        <v>0.133922963530434</v>
+        <v>0.24782208879099</v>
       </c>
     </row>
     <row r="10">
@@ -2750,10 +2750,10 @@
         <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>1.29799954436803</v>
+        <v>1.33471048462998</v>
       </c>
       <c r="D10" t="n">
-        <v>0.129395389458201</v>
+        <v>0.133102005324912</v>
       </c>
     </row>
     <row r="11">
@@ -2761,13 +2761,13 @@
         <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1.26256999925341</v>
+        <v>1.2784152462409</v>
       </c>
       <c r="D11" t="n">
-        <v>0.099603684188482</v>
+        <v>0.0538623176088768</v>
       </c>
     </row>
     <row r="12">
@@ -2775,13 +2775,13 @@
         <v>137</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>1.24400331049586</v>
+        <v>1.23462477669768</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0523634635522244</v>
+        <v>0.0957746181585188</v>
       </c>
     </row>
     <row r="13">
@@ -2792,10 +2792,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>1.01589747478353</v>
+        <v>1.0419230223091</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0317534985613793</v>
+        <v>0.0325945325146695</v>
       </c>
     </row>
     <row r="14">
@@ -2806,10 +2806,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0.93874003799178</v>
+        <v>0.966099224569711</v>
       </c>
       <c r="D14" t="n">
-        <v>0.20137946474707</v>
+        <v>0.207240653025551</v>
       </c>
     </row>
     <row r="15">
@@ -2820,10 +2820,10 @@
         <v>30</v>
       </c>
       <c r="C15" t="n">
-        <v>0.88838831221431</v>
+        <v>0.91450619339279</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0727289579438268</v>
+        <v>0.0747942235899131</v>
       </c>
     </row>
     <row r="16">
@@ -2834,10 +2834,10 @@
         <v>45</v>
       </c>
       <c r="C16" t="n">
-        <v>0.882167021634478</v>
+        <v>0.906566551686923</v>
       </c>
       <c r="D16" t="n">
-        <v>0.10313621526802</v>
+        <v>0.106006929239104</v>
       </c>
     </row>
     <row r="17">
@@ -2848,10 +2848,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>0.830670338738606</v>
+        <v>0.823828086395262</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0391804644561111</v>
+        <v>0.0379236148869747</v>
       </c>
     </row>
     <row r="18">
@@ -2862,10 +2862,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>0.574992210778144</v>
+        <v>0.591737275113773</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0178507863038453</v>
+        <v>0.0183715125881757</v>
       </c>
     </row>
     <row r="19">
@@ -2876,10 +2876,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>0.534461934066349</v>
+        <v>0.544923648873858</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0370712932226058</v>
+        <v>0.0379783822096945</v>
       </c>
     </row>
     <row r="20">
@@ -2890,10 +2890,10 @@
         <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.508321467184946</v>
+        <v>0.521954499957978</v>
       </c>
       <c r="D20" t="n">
-        <v>0.183697148295104</v>
+        <v>0.188788279689674</v>
       </c>
     </row>
     <row r="21">
@@ -2904,7 +2904,7 @@
         <v>86</v>
       </c>
       <c r="C21" t="n">
-        <v>0.48981849442218</v>
+        <v>0.50333145068083</v>
       </c>
       <c r="D21"/>
     </row>
@@ -2913,13 +2913,13 @@
         <v>137</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>0.33359594406187</v>
+        <v>0.339848494041903</v>
       </c>
       <c r="D22" t="n">
-        <v>0.187423957486608</v>
+        <v>0.00930666554020572</v>
       </c>
     </row>
     <row r="23">
@@ -2927,13 +2927,13 @@
         <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C23" t="n">
-        <v>0.331800077446703</v>
+        <v>0.320642253229683</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00909571256979151</v>
+        <v>0.179791727904061</v>
       </c>
     </row>
     <row r="24">
@@ -2944,10 +2944,10 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>0.308496113253229</v>
+        <v>0.305189120498422</v>
       </c>
       <c r="D24" t="n">
-        <v>0.11836813049791</v>
+        <v>0.116824635674158</v>
       </c>
     </row>
     <row r="25">
@@ -2958,10 +2958,10 @@
         <v>52</v>
       </c>
       <c r="C25" t="n">
-        <v>0.269376189208359</v>
+        <v>0.268566736272459</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0361749133342765</v>
+        <v>0.0351811649083005</v>
       </c>
     </row>
     <row r="26">
@@ -2972,10 +2972,10 @@
         <v>40</v>
       </c>
       <c r="C26" t="n">
-        <v>0.216312174752994</v>
+        <v>0.224192594211463</v>
       </c>
       <c r="D26" t="n">
-        <v>0.150303783328964</v>
+        <v>0.155778685660109</v>
       </c>
     </row>
     <row r="27">
@@ -2986,10 +2986,10 @@
         <v>119</v>
       </c>
       <c r="C27" t="n">
-        <v>0.211401947544266</v>
+        <v>0.217238185462835</v>
       </c>
       <c r="D27" t="n">
-        <v>0.119972981331922</v>
+        <v>0.123281566000562</v>
       </c>
     </row>
     <row r="28">
@@ -3000,10 +3000,10 @@
         <v>18</v>
       </c>
       <c r="C28" t="n">
-        <v>0.180355056520858</v>
+        <v>0.185729549279706</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0365648254978788</v>
+        <v>0.0376039702300224</v>
       </c>
     </row>
     <row r="29">
@@ -3014,10 +3014,10 @@
         <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>0.169397192609729</v>
+        <v>0.175121175011081</v>
       </c>
       <c r="D29" t="n">
-        <v>0.024816891369452</v>
+        <v>0.0256907212718145</v>
       </c>
     </row>
     <row r="30">
@@ -3028,10 +3028,10 @@
         <v>76</v>
       </c>
       <c r="C30" t="n">
-        <v>0.157610669714087</v>
+        <v>0.161233460630196</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00539666022118281</v>
+        <v>0.00548458040232496</v>
       </c>
     </row>
     <row r="31">
@@ -3042,10 +3042,10 @@
         <v>20</v>
       </c>
       <c r="C31" t="n">
-        <v>0.139142977708765</v>
+        <v>0.143136185577192</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0411837272476939</v>
+        <v>0.0423532235789516</v>
       </c>
     </row>
     <row r="32">
@@ -3056,10 +3056,10 @@
         <v>104</v>
       </c>
       <c r="C32" t="n">
-        <v>0.13197700535502</v>
+        <v>0.136686868796206</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0871230818978306</v>
+        <v>0.0902716506716733</v>
       </c>
     </row>
     <row r="33">
@@ -3067,13 +3067,13 @@
         <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C33" t="n">
-        <v>0.129676501040113</v>
+        <v>0.132439250367211</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0332930272528846</v>
+        <v>0.028157112730415</v>
       </c>
     </row>
     <row r="34">
@@ -3081,13 +3081,13 @@
         <v>137</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C34" t="n">
-        <v>0.12829060501765</v>
+        <v>0.128017576320275</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0272482899684345</v>
+        <v>0.0151863051303758</v>
       </c>
     </row>
     <row r="35">
@@ -3095,13 +3095,13 @@
         <v>137</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.124291651104395</v>
+        <v>0.126585690794578</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0147481334406228</v>
+        <v>0.0319608864979259</v>
       </c>
     </row>
     <row r="36">
@@ -3112,10 +3112,10 @@
         <v>63</v>
       </c>
       <c r="C36" t="n">
-        <v>0.110804923348842</v>
+        <v>0.110648809703401</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0131165689460771</v>
+        <v>0.0127303280820501</v>
       </c>
     </row>
     <row r="37">
@@ -3123,13 +3123,13 @@
         <v>137</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C37" t="n">
-        <v>0.109550262382671</v>
+        <v>0.107991139742958</v>
       </c>
       <c r="D37" t="n">
-        <v>0.025280811939818</v>
+        <v>0.0410110682613569</v>
       </c>
     </row>
     <row r="38">
@@ -3137,13 +3137,13 @@
         <v>137</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C38" t="n">
-        <v>0.10491414852157</v>
+        <v>0.106884759265806</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0398425121150081</v>
+        <v>0.0241702592492542</v>
       </c>
     </row>
     <row r="39">
@@ -3154,10 +3154,10 @@
         <v>69</v>
       </c>
       <c r="C39" t="n">
-        <v>0.103479046666588</v>
+        <v>0.106085726739919</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0165424487662633</v>
+        <v>0.0170466142455405</v>
       </c>
     </row>
     <row r="40">
@@ -3168,10 +3168,10 @@
         <v>21</v>
       </c>
       <c r="C40" t="n">
-        <v>0.100465496595539</v>
+        <v>0.098632358553192</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0314307977775608</v>
+        <v>0.0305681446454847</v>
       </c>
     </row>
     <row r="41">
@@ -3182,10 +3182,10 @@
         <v>13</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0917929832411444</v>
+        <v>0.0944694532038789</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0128657661664575</v>
+        <v>0.0132417821409677</v>
       </c>
     </row>
     <row r="42">
@@ -3193,13 +3193,13 @@
         <v>137</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0855498104004779</v>
+        <v>0.086594263181063</v>
       </c>
       <c r="D42" t="n">
-        <v>0.018952200334533</v>
+        <v>0.0371737281396527</v>
       </c>
     </row>
     <row r="43">
@@ -3207,13 +3207,13 @@
         <v>137</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0840533914081825</v>
+        <v>0.0844880398968756</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0362293004451723</v>
+        <v>0.0182260456200026</v>
       </c>
     </row>
     <row r="44">
@@ -3224,10 +3224,10 @@
         <v>29</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0808001311161664</v>
+        <v>0.0831656981832304</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0124291762203992</v>
+        <v>0.0127950783122685</v>
       </c>
     </row>
     <row r="45">
@@ -3238,10 +3238,10 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.076994197466267</v>
+        <v>0.0791553244756159</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0310143979014056</v>
+        <v>0.0318742477443166</v>
       </c>
     </row>
     <row r="46">
@@ -3252,10 +3252,10 @@
         <v>31</v>
       </c>
       <c r="C46" t="n">
-        <v>0.073951978123</v>
+        <v>0.0764200359304541</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00793441779774488</v>
+        <v>0.00821806387958583</v>
       </c>
     </row>
     <row r="47">
@@ -3263,13 +3263,13 @@
         <v>137</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0704477154272872</v>
+        <v>0.0691776989074485</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0480220743087568</v>
+        <v>0.00861548516550772</v>
       </c>
     </row>
     <row r="48">
@@ -3277,13 +3277,13 @@
         <v>137</v>
       </c>
       <c r="B48" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0682180066621407</v>
+        <v>0.0674992496203779</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0082996704743855</v>
+        <v>0.0458877574879519</v>
       </c>
     </row>
     <row r="49">
@@ -3294,10 +3294,10 @@
         <v>71</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0658028252583652</v>
+        <v>0.0673991450939971</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01588387726385</v>
+        <v>0.016329140662916</v>
       </c>
     </row>
     <row r="50">
@@ -3308,10 +3308,10 @@
         <v>51</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0510791646784403</v>
+        <v>0.0524943326513799</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0235840748727563</v>
+        <v>0.0242337124431185</v>
       </c>
     </row>
     <row r="51">
@@ -3322,10 +3322,10 @@
         <v>66</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0439528027273304</v>
+        <v>0.04528782884022</v>
       </c>
       <c r="D51" t="n">
-        <v>0.014658392215336</v>
+        <v>0.0151205499183107</v>
       </c>
     </row>
     <row r="52">
@@ -3336,10 +3336,10 @@
         <v>26</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0383163653007281</v>
+        <v>0.0394404619199695</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0116189930360815</v>
+        <v>0.0119605398360741</v>
       </c>
     </row>
     <row r="53">
@@ -3350,10 +3350,10 @@
         <v>101</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0369508888211304</v>
+        <v>0.0362801650282697</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00827203353783943</v>
+        <v>0.00790357386807797</v>
       </c>
     </row>
     <row r="54">
@@ -3364,10 +3364,10 @@
         <v>138</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0349958784907988</v>
+        <v>0.0362269563160493</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0163608948801383</v>
+        <v>0.0170000776384572</v>
       </c>
     </row>
     <row r="55">
@@ -3378,10 +3378,10 @@
         <v>11</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0338176884201133</v>
+        <v>0.0348238095072355</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00522647480687918</v>
+        <v>0.00537676581073555</v>
       </c>
     </row>
     <row r="56">
@@ -3392,10 +3392,10 @@
         <v>139</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0307403053368413</v>
+        <v>0.0316395837257462</v>
       </c>
       <c r="D56" t="n">
-        <v>0.015937825709771</v>
+        <v>0.0164036165034893</v>
       </c>
     </row>
     <row r="57">
@@ -3403,26 +3403,26 @@
         <v>137</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0283011353583534</v>
-      </c>
-      <c r="D57"/>
+        <v>0.0285018930213852</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.00775215744808481</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
         <v>137</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C58" t="n">
-        <v>0.027701596516703</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.00753967717787371</v>
-      </c>
+        <v>0.0270806492381326</v>
+      </c>
+      <c r="D58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
@@ -3432,7 +3432,7 @@
         <v>22</v>
       </c>
       <c r="C59" t="n">
-        <v>0.015617732312067</v>
+        <v>0.0161375110038096</v>
       </c>
       <c r="D59"/>
     </row>
@@ -3444,10 +3444,10 @@
         <v>77</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0138411150653884</v>
+        <v>0.0142471888332759</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0017127707614488</v>
+        <v>0.00176287756782357</v>
       </c>
     </row>
     <row r="61">
@@ -3458,10 +3458,10 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0137641175914339</v>
+        <v>0.0141660230010753</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00131602250930555</v>
+        <v>0.0013553034120688</v>
       </c>
     </row>
     <row r="62">
@@ -3472,10 +3472,10 @@
         <v>56</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0134894776653377</v>
+        <v>0.0138718419514769</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0015631549446498</v>
+        <v>0.00160899961333783</v>
       </c>
     </row>
     <row r="63">
@@ -3486,10 +3486,10 @@
         <v>46</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0134196182550781</v>
+        <v>0.0138080516196511</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00173343212990119</v>
+        <v>0.00178651452543754</v>
       </c>
     </row>
     <row r="64">
@@ -3500,10 +3500,10 @@
         <v>125</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0124426396683816</v>
+        <v>0.0128076075842298</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00439911675673076</v>
+        <v>0.00452817308679258</v>
       </c>
     </row>
     <row r="65">
@@ -3514,10 +3514,10 @@
         <v>47</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0120416209096549</v>
+        <v>0.0123957060165212</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00382967263799561</v>
+        <v>0.003941747770179</v>
       </c>
     </row>
     <row r="66">
@@ -3528,10 +3528,10 @@
         <v>53</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0114278644493336</v>
+        <v>0.0118009107735871</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00211364960345166</v>
+        <v>0.00215822850875124</v>
       </c>
     </row>
     <row r="67">
@@ -3542,10 +3542,10 @@
         <v>130</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00916264089186911</v>
+        <v>0.00942653962894426</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0028658944505364</v>
+        <v>0.00294672044371045</v>
       </c>
     </row>
     <row r="68">
@@ -3556,7 +3556,7 @@
         <v>140</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0089077769127309</v>
+        <v>0.00916903351093288</v>
       </c>
       <c r="D68"/>
     </row>
@@ -3568,10 +3568,10 @@
         <v>90</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00881667883754306</v>
+        <v>0.00907013144132543</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00332298168777018</v>
+        <v>0.00341833606605476</v>
       </c>
     </row>
     <row r="70">
@@ -3582,10 +3582,10 @@
         <v>83</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00869187974032043</v>
+        <v>0.00898493737893408</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00194692079877922</v>
+        <v>0.00203098630084255</v>
       </c>
     </row>
     <row r="71">
@@ -3596,7 +3596,7 @@
         <v>87</v>
       </c>
       <c r="C71" t="n">
-        <v>0.00732417992940791</v>
+        <v>0.0075438530589213</v>
       </c>
       <c r="D71"/>
     </row>
@@ -3608,10 +3608,10 @@
         <v>81</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00654267897225705</v>
+        <v>0.00673375793072019</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0025177290662893</v>
+        <v>0.00258633710669327</v>
       </c>
     </row>
     <row r="73">
@@ -3622,10 +3622,10 @@
         <v>48</v>
       </c>
       <c r="C73" t="n">
-        <v>0.00605898739385126</v>
+        <v>0.00623491873829889</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00104533368521172</v>
+        <v>0.00107421123177737</v>
       </c>
     </row>
     <row r="74">
@@ -3636,7 +3636,7 @@
         <v>108</v>
       </c>
       <c r="C74" t="n">
-        <v>0.00565574530380981</v>
+        <v>0.00582163434530094</v>
       </c>
       <c r="D74"/>
     </row>
@@ -3648,7 +3648,7 @@
         <v>85</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00428681680980228</v>
+        <v>0.00441079181313773</v>
       </c>
       <c r="D75"/>
     </row>
@@ -3660,10 +3660,10 @@
         <v>72</v>
       </c>
       <c r="C76" t="n">
-        <v>0.00398268848942568</v>
+        <v>0.00409785243787524</v>
       </c>
       <c r="D76" t="n">
-        <v>0.000436981159106562</v>
+        <v>0.000449912059585068</v>
       </c>
     </row>
     <row r="77">
@@ -3674,7 +3674,7 @@
         <v>64</v>
       </c>
       <c r="C77" t="n">
-        <v>0.00353486275565068</v>
+        <v>0.00363851395045826</v>
       </c>
       <c r="D77"/>
     </row>
@@ -3686,7 +3686,7 @@
         <v>78</v>
       </c>
       <c r="C78" t="n">
-        <v>0.00310429709392476</v>
+        <v>0.00318993745116269</v>
       </c>
       <c r="D78"/>
     </row>
@@ -3698,10 +3698,10 @@
         <v>39</v>
       </c>
       <c r="C79" t="n">
-        <v>0.00270579421010695</v>
+        <v>0.00278434878151413</v>
       </c>
       <c r="D79" t="n">
-        <v>0.000487424423054235</v>
+        <v>0.000502086754441095</v>
       </c>
     </row>
     <row r="80">
@@ -3712,7 +3712,7 @@
         <v>141</v>
       </c>
       <c r="C80" t="n">
-        <v>0.00268648633289951</v>
+        <v>0.00276528984165665</v>
       </c>
       <c r="D80"/>
     </row>
@@ -3724,7 +3724,7 @@
         <v>134</v>
       </c>
       <c r="C81" t="n">
-        <v>0.00253477322502408</v>
+        <v>0.00261468213079545</v>
       </c>
       <c r="D81"/>
     </row>
@@ -3736,10 +3736,10 @@
         <v>55</v>
       </c>
       <c r="C82" t="n">
-        <v>0.00216973732836583</v>
+        <v>0.00223338308796842</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0000654503645140934</v>
+        <v>0.0000673835280772706</v>
       </c>
     </row>
     <row r="83">
@@ -3750,10 +3750,10 @@
         <v>115</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0021594397938552</v>
+        <v>0.00222442478500701</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00047263272073894</v>
+        <v>0.00048533145522405</v>
       </c>
     </row>
     <row r="84">
@@ -3764,7 +3764,7 @@
         <v>142</v>
       </c>
       <c r="C84" t="n">
-        <v>0.00149103619016489</v>
+        <v>0.00153806245878289</v>
       </c>
       <c r="D84"/>
     </row>
@@ -3776,7 +3776,7 @@
         <v>114</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00104373703485919</v>
+        <v>0.00107661967201256</v>
       </c>
       <c r="D85"/>
     </row>
@@ -3788,7 +3788,7 @@
         <v>110</v>
       </c>
       <c r="C86" t="n">
-        <v>0.000989733487397163</v>
+        <v>0.00101878150121476</v>
       </c>
       <c r="D86"/>
     </row>
@@ -3800,7 +3800,7 @@
         <v>92</v>
       </c>
       <c r="C87" t="n">
-        <v>0.000886933668447245</v>
+        <v>0.000911402111355245</v>
       </c>
       <c r="D87"/>
     </row>
@@ -3812,7 +3812,7 @@
         <v>127</v>
       </c>
       <c r="C88" t="n">
-        <v>0.000745518095082446</v>
+        <v>0.000769031229391446</v>
       </c>
       <c r="D88"/>
     </row>
@@ -3824,7 +3824,7 @@
         <v>68</v>
       </c>
       <c r="C89" t="n">
-        <v>0.000282772638010788</v>
+        <v>0.000291054661987647</v>
       </c>
       <c r="D89"/>
     </row>
@@ -3861,10 +3861,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>21.9787154411997</v>
+        <v>21.9799582045037</v>
       </c>
       <c r="D2" t="n">
-        <v>0.490836988744614</v>
+        <v>0.490888986996894</v>
       </c>
     </row>
     <row r="3">
@@ -3875,10 +3875,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>8.76692677984079</v>
+        <v>8.76657567358605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.199941940599583</v>
+        <v>0.201058681955327</v>
       </c>
     </row>
     <row r="4">
@@ -3889,10 +3889,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>8.37598650030049</v>
+        <v>8.37538719628584</v>
       </c>
       <c r="D4" t="n">
-        <v>0.184735816032211</v>
+        <v>0.184717350896407</v>
       </c>
     </row>
     <row r="5">
@@ -3903,10 +3903,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>4.7955500050665</v>
+        <v>4.79608639224169</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0954406827325604</v>
+        <v>0.0954508015339451</v>
       </c>
     </row>
     <row r="6">
@@ -3917,10 +3917,10 @@
         <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>4.58632514697018</v>
+        <v>4.58631644613354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.265096385530426</v>
+        <v>0.265091787475345</v>
       </c>
     </row>
     <row r="7">
@@ -3931,10 +3931,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.96489566136487</v>
+        <v>3.96522201435841</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0964690180953352</v>
+        <v>0.0964813776637118</v>
       </c>
     </row>
     <row r="8">
@@ -3945,10 +3945,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7243080649101</v>
+        <v>3.72399152550915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.053899320325139</v>
+        <v>0.0538939796108262</v>
       </c>
     </row>
     <row r="9">
@@ -3959,10 +3959,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>3.66690114156154</v>
+        <v>3.66666827455714</v>
       </c>
       <c r="D9" t="n">
-        <v>0.140760881755757</v>
+        <v>0.140747505819984</v>
       </c>
     </row>
     <row r="10">
@@ -3973,10 +3973,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>3.57051007852822</v>
+        <v>3.57038310021036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0674328441142328</v>
+        <v>0.0674305129007403</v>
       </c>
     </row>
     <row r="11">
@@ -3987,10 +3987,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>3.21105032549323</v>
+        <v>3.21110959330595</v>
       </c>
       <c r="D11" t="n">
-        <v>0.429298584230496</v>
+        <v>0.429309077052021</v>
       </c>
     </row>
     <row r="12">
@@ -4001,10 +4001,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>3.18513984798712</v>
+        <v>3.18497137478922</v>
       </c>
       <c r="D12" t="n">
-        <v>0.114016331705178</v>
+        <v>0.114008461300709</v>
       </c>
     </row>
     <row r="13">
@@ -4015,10 +4015,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>3.04891292336428</v>
+        <v>3.04910811408604</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0562950685147359</v>
+        <v>0.0562993834594735</v>
       </c>
     </row>
     <row r="14">
@@ -4029,10 +4029,10 @@
         <v>44</v>
       </c>
       <c r="C14" t="n">
-        <v>2.90693837065784</v>
+        <v>2.9078237697701</v>
       </c>
       <c r="D14" t="n">
-        <v>0.848514761712234</v>
+        <v>0.848774383302174</v>
       </c>
     </row>
     <row r="15">
@@ -4043,10 +4043,10 @@
         <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>1.83886542492783</v>
+        <v>1.83873120338501</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0330914423985603</v>
+        <v>0.033088796804791</v>
       </c>
     </row>
     <row r="16">
@@ -4057,10 +4057,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>1.75106759017128</v>
+        <v>1.75138898300309</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1667718000852</v>
+        <v>0.166801682503198</v>
       </c>
     </row>
     <row r="17">
@@ -4071,10 +4071,10 @@
         <v>41</v>
       </c>
       <c r="C17" t="n">
-        <v>1.55734061781472</v>
+        <v>1.55728726615353</v>
       </c>
       <c r="D17" t="n">
-        <v>0.522080141675004</v>
+        <v>0.522067960073351</v>
       </c>
     </row>
     <row r="18">
@@ -4085,10 +4085,10 @@
         <v>46</v>
       </c>
       <c r="C18" t="n">
-        <v>1.48377840736855</v>
+        <v>1.48385256396774</v>
       </c>
       <c r="D18" t="n">
-        <v>0.122826069081501</v>
+        <v>0.122840981953677</v>
       </c>
     </row>
     <row r="19">
@@ -4099,10 +4099,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>1.23047170899452</v>
+        <v>1.230360372418</v>
       </c>
       <c r="D19" t="n">
-        <v>0.151613823845976</v>
+        <v>0.151602610044505</v>
       </c>
     </row>
     <row r="20">
@@ -4113,10 +4113,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1616757331315</v>
+        <v>1.16178318287229</v>
       </c>
       <c r="D20" t="n">
-        <v>0.176434462685899</v>
+        <v>0.176455029969349</v>
       </c>
     </row>
     <row r="21">
@@ -4127,10 +4127,10 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>1.09703163996876</v>
+        <v>1.0953890090959</v>
       </c>
       <c r="D21" t="n">
-        <v>0.126910254393261</v>
+        <v>0.134578545684737</v>
       </c>
     </row>
     <row r="22">
@@ -4141,10 +4141,10 @@
         <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>0.968131272611667</v>
+        <v>0.96806432673786</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0185739043304981</v>
+        <v>0.0185721689859961</v>
       </c>
     </row>
     <row r="23">
@@ -4155,10 +4155,10 @@
         <v>47</v>
       </c>
       <c r="C23" t="n">
-        <v>0.857836275493774</v>
+        <v>0.857814410525154</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0857934487131631</v>
+        <v>0.0857903118571765</v>
       </c>
     </row>
     <row r="24">
@@ -4169,10 +4169,10 @@
         <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>0.848467110325538</v>
+        <v>0.84830527092907</v>
       </c>
       <c r="D24" t="n">
-        <v>0.289379225813157</v>
+        <v>0.289314746281158</v>
       </c>
     </row>
     <row r="25">
@@ -4183,10 +4183,10 @@
         <v>45</v>
       </c>
       <c r="C25" t="n">
-        <v>0.818459234610933</v>
+        <v>0.818617242566109</v>
       </c>
       <c r="D25" t="n">
-        <v>0.067497634553842</v>
+        <v>0.067509913679081</v>
       </c>
     </row>
     <row r="26">
@@ -4197,10 +4197,10 @@
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>0.808472130103592</v>
+        <v>0.80850725443698</v>
       </c>
       <c r="D26" t="n">
-        <v>0.154569455135979</v>
+        <v>0.154585340843082</v>
       </c>
     </row>
     <row r="27">
@@ -4211,10 +4211,10 @@
         <v>77</v>
       </c>
       <c r="C27" t="n">
-        <v>0.745095754293287</v>
+        <v>0.745126362573919</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0231663501894589</v>
+        <v>0.0231683694809714</v>
       </c>
     </row>
     <row r="28">
@@ -4225,10 +4225,10 @@
         <v>37</v>
       </c>
       <c r="C28" t="n">
-        <v>0.717789083657777</v>
+        <v>0.717720333482241</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0904521077802339</v>
+        <v>0.0904446384621796</v>
       </c>
     </row>
     <row r="29">
@@ -4239,10 +4239,10 @@
         <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>0.546939917718448</v>
+        <v>0.5469106672692</v>
       </c>
       <c r="D29" t="n">
-        <v>0.236708808884444</v>
+        <v>0.23669411707758</v>
       </c>
     </row>
     <row r="30">
@@ -4253,10 +4253,10 @@
         <v>24</v>
       </c>
       <c r="C30" t="n">
-        <v>0.528952935250389</v>
+        <v>0.529021771158293</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0193981835922004</v>
+        <v>0.0194002915741415</v>
       </c>
     </row>
     <row r="31">
@@ -4267,10 +4267,10 @@
         <v>22</v>
       </c>
       <c r="C31" t="n">
-        <v>0.430293030354796</v>
+        <v>0.430362935082194</v>
       </c>
       <c r="D31" t="n">
-        <v>0.106578730709796</v>
+        <v>0.106595560404305</v>
       </c>
     </row>
     <row r="32">
@@ -4281,10 +4281,10 @@
         <v>52</v>
       </c>
       <c r="C32" t="n">
-        <v>0.419048522431741</v>
+        <v>0.419020322211645</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0232657073408555</v>
+        <v>0.0232625777419894</v>
       </c>
     </row>
     <row r="33">
@@ -4295,10 +4295,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="n">
-        <v>0.385966495665358</v>
+        <v>0.386046041583528</v>
       </c>
       <c r="D33" t="n">
-        <v>0.022520171705642</v>
+        <v>0.0225260377604896</v>
       </c>
     </row>
     <row r="34">
@@ -4309,10 +4309,10 @@
         <v>76</v>
       </c>
       <c r="C34" t="n">
-        <v>0.346401561761411</v>
+        <v>0.346406996330817</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00848242083577107</v>
+        <v>0.00848308271124754</v>
       </c>
     </row>
     <row r="35">
@@ -4323,10 +4323,10 @@
         <v>60</v>
       </c>
       <c r="C35" t="n">
-        <v>0.336323276074375</v>
+        <v>0.336320017196861</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0303813994566529</v>
+        <v>0.0303835110090498</v>
       </c>
     </row>
     <row r="36">
@@ -4337,10 +4337,10 @@
         <v>71</v>
       </c>
       <c r="C36" t="n">
-        <v>0.316077690942096</v>
+        <v>0.316104971437568</v>
       </c>
       <c r="D36" t="n">
-        <v>0.010231484938941</v>
+        <v>0.0102324518680789</v>
       </c>
     </row>
     <row r="37">
@@ -4351,10 +4351,10 @@
         <v>55</v>
       </c>
       <c r="C37" t="n">
-        <v>0.310150166875274</v>
+        <v>0.310114714012385</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0685769544517772</v>
+        <v>0.0685672363066828</v>
       </c>
     </row>
     <row r="38">
@@ -4365,10 +4365,10 @@
         <v>31</v>
       </c>
       <c r="C38" t="n">
-        <v>0.295566559308626</v>
+        <v>0.295571086745162</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00808169739661992</v>
+        <v>0.00808183984791037</v>
       </c>
     </row>
     <row r="39">
@@ -4379,10 +4379,10 @@
         <v>39</v>
       </c>
       <c r="C39" t="n">
-        <v>0.242674225434993</v>
+        <v>0.242650323142323</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0224444037160852</v>
+        <v>0.0224418613647339</v>
       </c>
     </row>
     <row r="40">
@@ -4393,10 +4393,10 @@
         <v>36</v>
       </c>
       <c r="C40" t="n">
-        <v>0.235791615880213</v>
+        <v>0.235759726724195</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0947939764946072</v>
+        <v>0.0947801490926459</v>
       </c>
     </row>
     <row r="41">
@@ -4407,10 +4407,10 @@
         <v>72</v>
       </c>
       <c r="C41" t="n">
-        <v>0.226671778921371</v>
+        <v>0.226639648319221</v>
       </c>
       <c r="D41" t="n">
-        <v>0.030802944107052</v>
+        <v>0.0307982994618997</v>
       </c>
     </row>
     <row r="42">
@@ -4421,10 +4421,10 @@
         <v>18</v>
       </c>
       <c r="C42" t="n">
-        <v>0.217412479600799</v>
+        <v>0.217459208654182</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0357391999950631</v>
+        <v>0.0357468425513277</v>
       </c>
     </row>
     <row r="43">
@@ -4435,10 +4435,10 @@
         <v>63</v>
       </c>
       <c r="C43" t="n">
-        <v>0.215133548017827</v>
+        <v>0.215139633004419</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00765016869487261</v>
+        <v>0.00765023903483435</v>
       </c>
     </row>
     <row r="44">
@@ -4449,10 +4449,10 @@
         <v>115</v>
       </c>
       <c r="C44" t="n">
-        <v>0.214486460596688</v>
+        <v>0.214470579235682</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0387518958895776</v>
+        <v>0.0387484901861466</v>
       </c>
     </row>
     <row r="45">
@@ -4463,10 +4463,10 @@
         <v>65</v>
       </c>
       <c r="C45" t="n">
-        <v>0.213394528600517</v>
+        <v>0.213419785319753</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0615196028841004</v>
+        <v>0.0615402836652481</v>
       </c>
     </row>
     <row r="46">
@@ -4477,10 +4477,10 @@
         <v>29</v>
       </c>
       <c r="C46" t="n">
-        <v>0.188935625579661</v>
+        <v>0.188942846136338</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0106093756356102</v>
+        <v>0.0106093439118613</v>
       </c>
     </row>
     <row r="47">
@@ -4491,10 +4491,10 @@
         <v>26</v>
       </c>
       <c r="C47" t="n">
-        <v>0.184825372319607</v>
+        <v>0.18480018114175</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0604408082587919</v>
+        <v>0.0604306433345011</v>
       </c>
     </row>
     <row r="48">
@@ -4505,10 +4505,10 @@
         <v>38</v>
       </c>
       <c r="C48" t="n">
-        <v>0.182669834283909</v>
+        <v>0.182662735135597</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0274990566320673</v>
+        <v>0.0275001011227362</v>
       </c>
     </row>
     <row r="49">
@@ -4519,10 +4519,10 @@
         <v>69</v>
       </c>
       <c r="C49" t="n">
-        <v>0.149037282460456</v>
+        <v>0.149033893417521</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00490041538477011</v>
+        <v>0.00490041359945902</v>
       </c>
     </row>
     <row r="50">
@@ -4533,10 +4533,10 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>0.13028445282164</v>
+        <v>0.130277976533951</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0132887801066265</v>
+        <v>0.0132870685725215</v>
       </c>
     </row>
     <row r="51">
@@ -4547,10 +4547,10 @@
         <v>28</v>
       </c>
       <c r="C51" t="n">
-        <v>0.118686057287232</v>
+        <v>0.118722903980699</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0288540778614486</v>
+        <v>0.0288633279015669</v>
       </c>
     </row>
     <row r="52">
@@ -4561,10 +4561,10 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>0.114909437458452</v>
+        <v>0.114891980988895</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0178909320574738</v>
+        <v>0.0178852675083426</v>
       </c>
     </row>
     <row r="53">
@@ -4575,10 +4575,10 @@
         <v>21</v>
       </c>
       <c r="C53" t="n">
-        <v>0.109250748394383</v>
+        <v>0.109268448100416</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0156842513821768</v>
+        <v>0.0156864711753446</v>
       </c>
     </row>
     <row r="54">
@@ -4589,7 +4589,7 @@
         <v>43</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0989603543565518</v>
+        <v>0.0989321799505745</v>
       </c>
       <c r="D54"/>
     </row>
@@ -4601,10 +4601,10 @@
         <v>85</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0931332790647367</v>
+        <v>0.0931309996902721</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0327415527241503</v>
+        <v>0.0327398335275147</v>
       </c>
     </row>
     <row r="56">
@@ -4615,10 +4615,10 @@
         <v>64</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0904120440215771</v>
+        <v>0.0904003250131124</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00899418206847615</v>
+        <v>0.00899305994560171</v>
       </c>
     </row>
     <row r="57">
@@ -4629,7 +4629,7 @@
         <v>32</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0828081315444811</v>
+        <v>0.082792415700007</v>
       </c>
       <c r="D57"/>
     </row>
@@ -4641,10 +4641,10 @@
         <v>80</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0774329262628541</v>
+        <v>0.0774453642762558</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00543996167827075</v>
+        <v>0.00544061141138761</v>
       </c>
     </row>
     <row r="59">
@@ -4655,10 +4655,10 @@
         <v>90</v>
       </c>
       <c r="C59" t="n">
-        <v>0.07513007830488</v>
+        <v>0.0751270586034985</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00978986799512828</v>
+        <v>0.00978935660872495</v>
       </c>
     </row>
     <row r="60">
@@ -4669,10 +4669,10 @@
         <v>48</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0597653768784115</v>
+        <v>0.059774455983255</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00368020830547326</v>
+        <v>0.00368083984263925</v>
       </c>
     </row>
     <row r="61">
@@ -4683,10 +4683,10 @@
         <v>107</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0555176044620979</v>
+        <v>0.0555219006253551</v>
       </c>
       <c r="D61" t="n">
-        <v>0.010882824261015</v>
+        <v>0.0108834020325943</v>
       </c>
     </row>
     <row r="62">
@@ -4697,10 +4697,10 @@
         <v>101</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0554446595183428</v>
+        <v>0.0554444320279701</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00370121646356186</v>
+        <v>0.00370068759532628</v>
       </c>
     </row>
     <row r="63">
@@ -4711,10 +4711,10 @@
         <v>100</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0530687171392698</v>
+        <v>0.0530674085948034</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00649743587405406</v>
+        <v>0.00649680300087323</v>
       </c>
     </row>
     <row r="64">
@@ -4725,10 +4725,10 @@
         <v>92</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0510835085367868</v>
+        <v>0.0510840033290636</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00409622825963514</v>
+        <v>0.00409602160930587</v>
       </c>
     </row>
     <row r="65">
@@ -4739,10 +4739,10 @@
         <v>74</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0472670529958941</v>
+        <v>0.0472737734920091</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00300145703035621</v>
+        <v>0.00300199852633558</v>
       </c>
     </row>
     <row r="66">
@@ -4753,10 +4753,10 @@
         <v>62</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0439272059655816</v>
+        <v>0.0439311193068667</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00281672021647584</v>
+        <v>0.00281725961473784</v>
       </c>
     </row>
     <row r="67">
@@ -4767,7 +4767,7 @@
         <v>87</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0425454373998597</v>
+        <v>0.0425428850299084</v>
       </c>
       <c r="D67"/>
     </row>
@@ -4779,10 +4779,10 @@
         <v>122</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0422022374185856</v>
+        <v>0.042212466894678</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00704739422470973</v>
+        <v>0.00704998638812337</v>
       </c>
     </row>
     <row r="69">
@@ -4793,10 +4793,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0401099282992982</v>
+        <v>0.0401154360391381</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00899770989979867</v>
+        <v>0.00899976873991183</v>
       </c>
     </row>
     <row r="70">
@@ -4807,10 +4807,10 @@
         <v>139</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0399729323137417</v>
+        <v>0.039965354638804</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0223933769823801</v>
+        <v>0.0223895389603966</v>
       </c>
     </row>
     <row r="71">
@@ -4821,10 +4821,10 @@
         <v>83</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0397407192602098</v>
+        <v>0.0397402698905676</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00804735726344126</v>
+        <v>0.00804510732230997</v>
       </c>
     </row>
     <row r="72">
@@ -4835,7 +4835,7 @@
         <v>78</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0390031233074237</v>
+        <v>0.0389926269564989</v>
       </c>
       <c r="D72"/>
     </row>
@@ -4847,10 +4847,10 @@
         <v>67</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0345293411473442</v>
+        <v>0.0345266407570089</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00520283223202059</v>
+        <v>0.00520217535474315</v>
       </c>
     </row>
     <row r="74">
@@ -4861,10 +4861,10 @@
         <v>84</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0345161871410933</v>
+        <v>0.0345189461904412</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00893760982438653</v>
+        <v>0.00893874389584192</v>
       </c>
     </row>
     <row r="75">
@@ -4875,10 +4875,10 @@
         <v>59</v>
       </c>
       <c r="C75" t="n">
-        <v>0.029074987612196</v>
+        <v>0.0290714171741318</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00673156812733868</v>
+        <v>0.00672960975019451</v>
       </c>
     </row>
     <row r="76">
@@ -4889,10 +4889,10 @@
         <v>125</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0265305095280331</v>
+        <v>0.0265273544123701</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00902388670407662</v>
+        <v>0.00902092654466737</v>
       </c>
     </row>
     <row r="77">
@@ -4903,10 +4903,10 @@
         <v>144</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0256911195041461</v>
+        <v>0.0256851355435961</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0171909980378978</v>
+        <v>0.0171872123055681</v>
       </c>
     </row>
     <row r="78">
@@ -4917,10 +4917,10 @@
         <v>99</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0250270664044901</v>
+        <v>0.0250266151135585</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00331625301899882</v>
+        <v>0.00331646493945638</v>
       </c>
     </row>
     <row r="79">
@@ -4931,10 +4931,10 @@
         <v>53</v>
       </c>
       <c r="C79" t="n">
-        <v>0.02468760335681</v>
+        <v>0.0246914905929518</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0039508930761767</v>
+        <v>0.00395200937404464</v>
       </c>
     </row>
     <row r="80">
@@ -4945,10 +4945,10 @@
         <v>61</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0240757178501265</v>
+        <v>0.0240772699490756</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00316824594110922</v>
+        <v>0.00316770989894922</v>
       </c>
     </row>
     <row r="81">
@@ -4959,10 +4959,10 @@
         <v>145</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0237037434801785</v>
+        <v>0.0237031496639221</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00682263226104706</v>
+        <v>0.00682189265494413</v>
       </c>
     </row>
     <row r="82">
@@ -4973,10 +4973,10 @@
         <v>121</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0222829613277351</v>
+        <v>0.0222802524851444</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00249317401432221</v>
+        <v>0.0024928912067423</v>
       </c>
     </row>
     <row r="83">
@@ -4987,10 +4987,10 @@
         <v>93</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0220213012374824</v>
+        <v>0.0220279005835373</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0143380396374616</v>
+        <v>0.0143421073785844</v>
       </c>
     </row>
     <row r="84">
@@ -5001,10 +5001,10 @@
         <v>81</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0219029899198959</v>
+        <v>0.0219035922459783</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00308503511636453</v>
+        <v>0.00308526430285486</v>
       </c>
     </row>
     <row r="85">
@@ -5015,10 +5015,10 @@
         <v>66</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0200565710310945</v>
+        <v>0.020054281611199</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00367870256286118</v>
+        <v>0.00367732895311549</v>
       </c>
     </row>
     <row r="86">
@@ -5029,10 +5029,10 @@
         <v>75</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0189050723134356</v>
+        <v>0.0189074176699697</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00270797388873265</v>
+        <v>0.00270831467486109</v>
       </c>
     </row>
     <row r="87">
@@ -5043,10 +5043,10 @@
         <v>97</v>
       </c>
       <c r="C87" t="n">
-        <v>0.015449903512412</v>
+        <v>0.0154465809187106</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00589527197923556</v>
+        <v>0.0058945862179202</v>
       </c>
     </row>
     <row r="88">
@@ -5057,10 +5057,10 @@
         <v>49</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0133806886427356</v>
+        <v>0.0133831671015731</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0011638019432493</v>
+        <v>0.0011639953494407</v>
       </c>
     </row>
     <row r="89">
@@ -5071,10 +5071,10 @@
         <v>68</v>
       </c>
       <c r="C89" t="n">
-        <v>0.012735768643081</v>
+        <v>0.0127365993963008</v>
       </c>
       <c r="D89" t="n">
-        <v>0.000804625879620015</v>
+        <v>0.00080439076786438</v>
       </c>
     </row>
     <row r="90">
@@ -5085,7 +5085,7 @@
         <v>146</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0115894268937818</v>
+        <v>0.0115854025923441</v>
       </c>
       <c r="D90"/>
     </row>
@@ -5097,10 +5097,10 @@
         <v>88</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0105078088343309</v>
+        <v>0.0105113755676532</v>
       </c>
       <c r="D91" t="n">
-        <v>0.000695693990503509</v>
+        <v>0.000696749609857311</v>
       </c>
     </row>
     <row r="92">
@@ -5111,7 +5111,7 @@
         <v>136</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0104810523897978</v>
+        <v>0.0104799249606146</v>
       </c>
       <c r="D92"/>
     </row>
@@ -5123,10 +5123,10 @@
         <v>91</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0104059400245581</v>
+        <v>0.0104062662942485</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00178480716024466</v>
+        <v>0.00178472513990436</v>
       </c>
     </row>
     <row r="94">
@@ -5137,10 +5137,10 @@
         <v>42</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0102809022265025</v>
+        <v>0.0102788203664386</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00662758978737952</v>
+        <v>0.00662641101662855</v>
       </c>
     </row>
     <row r="95">
@@ -5151,7 +5151,7 @@
         <v>147</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00880533662757085</v>
+        <v>0.00880743994783173</v>
       </c>
       <c r="D95"/>
     </row>
@@ -5163,10 +5163,10 @@
         <v>98</v>
       </c>
       <c r="C96" t="n">
-        <v>0.00829950529628536</v>
+        <v>0.00829750682753266</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00488196017629464</v>
+        <v>0.00488004694521971</v>
       </c>
     </row>
     <row r="97">
@@ -5177,10 +5177,10 @@
         <v>110</v>
       </c>
       <c r="C97" t="n">
-        <v>0.00751019018255811</v>
+        <v>0.00751056931079806</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00155233406502311</v>
+        <v>0.00155267126757225</v>
       </c>
     </row>
     <row r="98">
@@ -5191,7 +5191,7 @@
         <v>82</v>
       </c>
       <c r="C98" t="n">
-        <v>0.00730959158723154</v>
+        <v>0.00730789592149665</v>
       </c>
       <c r="D98"/>
     </row>
@@ -5203,10 +5203,10 @@
         <v>106</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0072583208583217</v>
+        <v>0.00725821740919093</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00165758289577762</v>
+        <v>0.00165753410433041</v>
       </c>
     </row>
     <row r="100">
@@ -5217,7 +5217,7 @@
         <v>114</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00650465609108132</v>
+        <v>0.00650168463607803</v>
       </c>
       <c r="D100"/>
     </row>
@@ -5229,10 +5229,10 @@
         <v>94</v>
       </c>
       <c r="C101" t="n">
-        <v>0.00460920863352648</v>
+        <v>0.00460949360120326</v>
       </c>
       <c r="D101" t="n">
-        <v>0.000478895956824243</v>
+        <v>0.000479108282563972</v>
       </c>
     </row>
     <row r="102">
@@ -5243,7 +5243,7 @@
         <v>141</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00418940151357515</v>
+        <v>0.00418838416681624</v>
       </c>
       <c r="D102"/>
     </row>
@@ -5255,7 +5255,7 @@
         <v>89</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00370255380494725</v>
+        <v>0.00370190826886904</v>
       </c>
       <c r="D103"/>
     </row>
@@ -5267,10 +5267,10 @@
         <v>119</v>
       </c>
       <c r="C104" t="n">
-        <v>0.00358528882876715</v>
+        <v>0.00358551861146706</v>
       </c>
       <c r="D104" t="n">
-        <v>0.000338815391567233</v>
+        <v>0.000338416431745612</v>
       </c>
     </row>
     <row r="105">
@@ -5281,10 +5281,10 @@
         <v>116</v>
       </c>
       <c r="C105" t="n">
-        <v>0.00339769476234774</v>
+        <v>0.00339711378735422</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00028522185253323</v>
+        <v>0.000284404844539178</v>
       </c>
     </row>
     <row r="106">
@@ -5295,7 +5295,7 @@
         <v>40</v>
       </c>
       <c r="C106" t="n">
-        <v>0.00311996585764075</v>
+        <v>0.00311854059579324</v>
       </c>
       <c r="D106"/>
     </row>
@@ -5307,7 +5307,7 @@
         <v>126</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00305726011193323</v>
+        <v>0.00305638642701374</v>
       </c>
       <c r="D107"/>
     </row>
@@ -5319,7 +5319,7 @@
         <v>124</v>
       </c>
       <c r="C108" t="n">
-        <v>0.00253401467009964</v>
+        <v>0.00253285708229416</v>
       </c>
       <c r="D108"/>
     </row>
@@ -5331,7 +5331,7 @@
         <v>148</v>
       </c>
       <c r="C109" t="n">
-        <v>0.00201293664975059</v>
+        <v>0.00201328707765308</v>
       </c>
       <c r="D109"/>
     </row>
@@ -5343,10 +5343,10 @@
         <v>112</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00199761522201514</v>
+        <v>0.00199834617169647</v>
       </c>
       <c r="D110" t="n">
-        <v>0.000186058412341193</v>
+        <v>0.000185877455545797</v>
       </c>
     </row>
     <row r="111">
@@ -5357,7 +5357,7 @@
         <v>149</v>
       </c>
       <c r="C111" t="n">
-        <v>0.001954640485684</v>
+        <v>0.00195471872630317</v>
       </c>
       <c r="D111"/>
     </row>
@@ -5369,10 +5369,10 @@
         <v>134</v>
       </c>
       <c r="C112" t="n">
-        <v>0.00178333944973448</v>
+        <v>0.00178379476215956</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000801020496358377</v>
+        <v>0.000801552583773679</v>
       </c>
     </row>
     <row r="113">
@@ -5383,7 +5383,7 @@
         <v>127</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00177541715051518</v>
+        <v>0.00177542785482386</v>
       </c>
       <c r="D113"/>
     </row>
@@ -5395,10 +5395,10 @@
         <v>135</v>
       </c>
       <c r="C114" t="n">
-        <v>0.00172227795480832</v>
+        <v>0.00172358291115443</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00017926116801792</v>
+        <v>0.00017928492614524</v>
       </c>
     </row>
     <row r="115">
@@ -5409,7 +5409,7 @@
         <v>142</v>
       </c>
       <c r="C115" t="n">
-        <v>0.00165785321964755</v>
+        <v>0.00165941172007079</v>
       </c>
       <c r="D115"/>
     </row>
@@ -5421,10 +5421,10 @@
         <v>35</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00151293493487176</v>
+        <v>0.00151224379639819</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00017263970465586</v>
+        <v>0.000172560839438855</v>
       </c>
     </row>
     <row r="117">
@@ -5435,7 +5435,7 @@
         <v>103</v>
       </c>
       <c r="C117" t="n">
-        <v>0.00139537100400414</v>
+        <v>0.00139600354805577</v>
       </c>
       <c r="D117"/>
     </row>
@@ -5447,7 +5447,7 @@
         <v>140</v>
       </c>
       <c r="C118" t="n">
-        <v>0.00124148407860272</v>
+        <v>0.00124091694422617</v>
       </c>
       <c r="D118"/>
     </row>
@@ -5459,10 +5459,10 @@
         <v>150</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00123647658758674</v>
+        <v>0.0012363599679094</v>
       </c>
       <c r="D119" t="n">
-        <v>0.000275550627961508</v>
+        <v>0.000275107806530468</v>
       </c>
     </row>
     <row r="120">
@@ -5473,10 +5473,10 @@
         <v>25</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00122093094383565</v>
+        <v>0.00122156847101236</v>
       </c>
       <c r="D120" t="n">
-        <v>0.000123347749455727</v>
+        <v>0.000123397049933789</v>
       </c>
     </row>
     <row r="121">
@@ -5487,7 +5487,7 @@
         <v>151</v>
       </c>
       <c r="C121" t="n">
-        <v>0.00112982450281364</v>
+        <v>0.0011293083767303</v>
       </c>
       <c r="D121"/>
     </row>
@@ -5499,7 +5499,7 @@
         <v>111</v>
       </c>
       <c r="C122" t="n">
-        <v>0.00110359122898367</v>
+        <v>0.00110308708677645</v>
       </c>
       <c r="D122"/>
     </row>
@@ -5511,10 +5511,10 @@
         <v>152</v>
       </c>
       <c r="C123" t="n">
-        <v>0.000875563541077049</v>
+        <v>0.000876209429825342</v>
       </c>
       <c r="D123" t="n">
-        <v>0.0000203465653558076</v>
+        <v>0.0000204429188032432</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>153</v>
       </c>
       <c r="C124" t="n">
-        <v>0.000633484982856941</v>
+        <v>0.000633195594441095</v>
       </c>
       <c r="D124"/>
     </row>
@@ -5537,7 +5537,7 @@
         <v>154</v>
       </c>
       <c r="C125" t="n">
-        <v>0.000523245441833582</v>
+        <v>0.000523529344719584</v>
       </c>
       <c r="D125"/>
     </row>
@@ -5549,7 +5549,7 @@
         <v>113</v>
       </c>
       <c r="C126" t="n">
-        <v>0.000452168964875471</v>
+        <v>0.00045256004142569</v>
       </c>
       <c r="D126"/>
     </row>
